--- a/led_sign/V2/BOM.xlsx
+++ b/led_sign/V2/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ambadran717/small_projects/led_sign/V2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B89806-FD88-514F-B5BF-3F6527AC6F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEFCF83-E1B2-914C-915C-5F613A76CD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="1280" windowWidth="22040" windowHeight="14340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
